--- a/tests/humedadGravimetrica1.xlsx
+++ b/tests/humedadGravimetrica1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t xml:space="preserve">DATOS DE Humedad Gravimétrica</t>
   </si>
@@ -31,31 +31,163 @@
     <t xml:space="preserve">Rep</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso capsula Vacía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso cápsula + suelo húmedo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso cápsula + suelo seco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperatura secado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiempo secado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97</t>
+    <t xml:space="preserve">Peso cápsula Vacía (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso cápsula + suelo húmedo (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso cápsula + suelo seco (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperatura secado (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo secado (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.05</t>
   </si>
 </sst>
 </file>
@@ -65,7 +197,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -90,6 +222,13 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -144,7 +283,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -161,8 +300,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -185,37 +332,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -288,7 +435,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -342,127 +489,472 @@
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>209</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>231</v>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>227</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>235</v>
+      <c r="B21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/tests/humedadGravimetrica1.xlsx
+++ b/tests/humedadGravimetrica1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
   <si>
     <t xml:space="preserve">DATOS DE Humedad Gravimétrica</t>
   </si>
@@ -46,16 +46,262 @@
     <t xml:space="preserve">Tiempo secado</t>
   </si>
   <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.38</t>
+    <t xml:space="preserve">12.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">248.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">239.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">247.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">238.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">245.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">241.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">234.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.2</t>
   </si>
   <si>
     <t xml:space="preserve">13.02</t>
   </si>
   <si>
+    <t xml:space="preserve">253.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">244.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">239.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">226.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">248.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">239.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">245.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">234.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.8</t>
   </si>
 </sst>
 </file>
@@ -185,37 +431,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -288,7 +534,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -350,9 +596,9 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
@@ -360,109 +606,661 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>209</v>
+        <v>105</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>233</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>1003</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>1004</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>235</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
